--- a/Documentation/Best For Lists/Best Pets for Remote Monitoring List.xlsx
+++ b/Documentation/Best For Lists/Best Pets for Remote Monitoring List.xlsx
@@ -614,7 +614,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-12  |  Products shown: 7  |  Eliminated by dedup rule: 5  |  Pre-filter: Type equal Ai &amp; Robotic Pets  (17 products removed)</t>
+          <t>Generated: 2026-07-15  |  Products shown: 7  |  Eliminated by dedup rule: 5  |  Pre-filter: Type equal Ai &amp; Robotic Pets  (17 products removed)</t>
         </is>
       </c>
     </row>

--- a/Documentation/Best For Lists/Best Pets for Remote Monitoring List.xlsx
+++ b/Documentation/Best For Lists/Best Pets for Remote Monitoring List.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -70,6 +70,12 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00185FA5"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00595959"/>
       <sz val="11"/>
     </font>
     <font>
@@ -149,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -191,16 +197,19 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -578,7 +587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U12"/>
+  <dimension ref="A1:U13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -614,7 +623,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-15  |  Products shown: 7  |  Eliminated by dedup rule: 5  |  Pre-filter: Type equal Ai &amp; Robotic Pets  (17 products removed)</t>
+          <t>Generated: 2026-07-15  |  Products shown: 8  |  Eliminated by dedup rule: 5  |  Pre-filter: Type equal Ai &amp; Robotic Pets  (16 products removed)</t>
         </is>
       </c>
     </row>
@@ -1316,6 +1325,79 @@
       <c r="U12" s="8" t="inlineStr">
         <is>
           <t>Breathing-only mechanism; no sensors, voice, or touch response. Sound Level Control=1 — no on/off switch or mute (battery must be removed to silence). Autonomous Interaction=3: breathing runs continuously without user direction. Review strength estimated; recommend manual verification. Black/white coat: high contrast, distinctive visibility. Product name updated: 'Original Black and White Shorthair Cat' per repo. Review Strength=4: 1200 reviews, 4.4★ (repo, 2026-06-22). SOUND QUALITY UPDATE (2026-07-01, Tim-confirmed): Perfect Petzzz is NOT silent — manufacturer FAQ confirms the breathing mechanism emits sound as normal operation, and multiple Amazon reviews describe a mechanical/grinding noise rather than a soothing breath. Sound Quality rescored from 2 to 2 under the new merged rubric (was previously scored under 'absence of sound = neutral' logic, now scored on actual sound character; net score unchanged at 2, but rationale corrected). Sound appears to vary unit to unit per manufacturer's own FAQ and mixed review reports (some units near-silent/subtle snore, others audibly grinding) — no per-unit review data available to differentiate individual SKUs, so all 8 Perfect Petzzz products scored uniformly at 2 pending any future unit-specific verification. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=5, Familiar Form=4, Safety=5, Calmness=avg(Sound=2, Behavioral Realism=1)=1.5. Raw average of 4 sub-criteria=3.88, rounded=4, Evidence Tier D cap=3 -&gt; Final=3 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="45" customHeight="1">
+      <c r="A13" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Wuffy</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>Wuffy Robot Puppy</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="n"/>
+      <c r="G13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="15" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="J13" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="L13" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="M13" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="N13" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="O13" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="P13" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q13" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="R13" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="S13" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" s="12" t="inlineStr">
+        <is>
+          <t>WARNING — LOW CONFIDENCE ACROSS ALL SCORES. No verified independent reviews found; all scores based on wuffyrobot.com marketing claims only. Review Strength=1: no verifiable third-party reviews identified. Brand Reliability=2: new/unverifiable brand, no established track record. Return/Gift Suitability=2: return policy unclear from DTC site. Recommend independent verification of product claims before featuring on site. Compare against Puppy Milow profile for scam-risk indicators. Review Strength=2: 80 reviews but only 3★ (repo data, 2026-06-22). Low rating confirms earlier caution flag about product quality/marketing claims. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=3, Familiar Form=3, Safety=4, Calmness=avg(Sound=2, Behavioral Realism=2)=2.0. Raw average of 4 sub-criteria=3.0, rounded=3, Evidence Tier D cap=3 -&gt; Final=3 (was 2). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1432,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>Eliminated by dedup rule — Best Pets for Remote Monitoring  (same Manufacturer x Price Category x Animal Category as a higher-scoring product)</t>
         </is>
@@ -1399,190 +1481,190 @@
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="16" t="inlineStr">
+      <c r="A3" s="17" t="inlineStr">
         <is>
           <t>Enabot</t>
         </is>
       </c>
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>EBO Air 2S FamilyBot</t>
         </is>
       </c>
-      <c r="C3" s="16" t="inlineStr">
+      <c r="C3" s="17" t="inlineStr">
         <is>
           <t>Premium</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
+      <c r="D3" s="17" t="inlineStr">
         <is>
           <t>Robot</t>
         </is>
       </c>
-      <c r="E3" s="16" t="n">
+      <c r="E3" s="17" t="n">
         <v>3.1</v>
       </c>
-      <c r="F3" s="16" t="n">
+      <c r="F3" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="G3" s="16" t="inlineStr">
+      <c r="G3" s="17" t="inlineStr">
         <is>
           <t>EBO Air 2 Plus FamilyBot</t>
         </is>
       </c>
-      <c r="H3" s="16" t="inlineStr">
+      <c r="H3" s="17" t="inlineStr">
         <is>
           <t>score=3.10 rating=5</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t>Enabot</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>EBO X FamilyBot</t>
         </is>
       </c>
-      <c r="C4" s="17" t="inlineStr">
+      <c r="C4" s="18" t="inlineStr">
         <is>
           <t>Premium</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="18" t="inlineStr">
         <is>
           <t>Robot</t>
         </is>
       </c>
-      <c r="E4" s="17" t="n">
+      <c r="E4" s="18" t="n">
         <v>3.1</v>
       </c>
-      <c r="F4" s="17" t="n">
+      <c r="F4" s="18" t="n">
         <v>4.5</v>
       </c>
-      <c r="G4" s="17" t="inlineStr">
+      <c r="G4" s="18" t="inlineStr">
         <is>
           <t>EBO Air 2 Plus FamilyBot</t>
         </is>
       </c>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="H4" s="18" t="inlineStr">
         <is>
           <t>score=3.10 rating=4.5</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>Perfect Petzzz</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>Original Beagle</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="E5" s="17" t="n">
         <v>3.1</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="F5" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="16" t="inlineStr">
+      <c r="G5" s="17" t="inlineStr">
         <is>
           <t>Original Black and White Shorthair Cat</t>
         </is>
       </c>
-      <c r="H5" s="16" t="inlineStr">
+      <c r="H5" s="17" t="inlineStr">
         <is>
           <t>score=3.10 rating=0</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="18" t="inlineStr">
         <is>
           <t>Perfect Petzzz</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>Original Shih Tzu</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="C6" s="18" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="18" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="E6" s="17" t="n">
+      <c r="E6" s="18" t="n">
         <v>3.1</v>
       </c>
-      <c r="F6" s="17" t="n">
+      <c r="F6" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="17" t="inlineStr">
+      <c r="G6" s="18" t="inlineStr">
         <is>
           <t>Original Black and White Shorthair Cat</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="H6" s="18" t="inlineStr">
         <is>
           <t>score=3.10 rating=0</t>
         </is>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>Enabot</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>ROLA Mini Pet Monitor</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>Best Value</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>Robot</t>
         </is>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="17" t="n">
         <v>2.7</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="F7" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="G7" s="17" t="inlineStr">
         <is>
           <t>EBO Air 2 FamilyBot</t>
         </is>
       </c>
-      <c r="H7" s="16" t="inlineStr">
+      <c r="H7" s="17" t="inlineStr">
         <is>
           <t>score=2.70 rating=5</t>
         </is>
@@ -1612,7 +1694,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="18" t="inlineStr">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t>Weights applied — Best Pets for Remote Monitoring</t>
         </is>
@@ -1626,154 +1708,154 @@
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="19" t="inlineStr">
+      <c r="A3" s="20" t="inlineStr">
         <is>
           <t>Feature (scores-file column)</t>
         </is>
       </c>
-      <c r="B3" s="19" t="inlineStr">
+      <c r="B3" s="20" t="inlineStr">
         <is>
           <t>Weight</t>
         </is>
       </c>
-      <c r="C3" s="19" t="inlineStr">
+      <c r="C3" s="20" t="inlineStr">
         <is>
           <t>What It Measures</t>
         </is>
       </c>
-      <c r="D3" s="19" t="inlineStr">
+      <c r="D3" s="20" t="inlineStr">
         <is>
           <t>Score Type</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="20" t="inlineStr">
+      <c r="A4" s="21" t="inlineStr">
         <is>
           <t>ai / advanced interaction level</t>
         </is>
       </c>
-      <c r="B4" s="20" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t>15%</t>
         </is>
       </c>
-      <c r="C4" s="20" t="inlineStr">
+      <c r="C4" s="21" t="inlineStr">
         <is>
           <t>Voice commands, learning behavior, app control, personality, sensors</t>
         </is>
       </c>
-      <c r="D4" s="20" t="inlineStr">
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t>1 – 5</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="22" t="inlineStr">
         <is>
           <t>brand / seller reliability</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr">
+      <c r="C5" s="22" t="inlineStr">
         <is>
           <t>Known brand, warranty, support, documentation, return policy</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="D5" s="22" t="inlineStr">
         <is>
           <t>1 – 5</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="20" t="inlineStr">
+      <c r="A6" s="21" t="inlineStr">
         <is>
           <t>charging convenience</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr">
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>Battery life, charging ease, self-charging capability</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t>1 – 5</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="21" t="inlineStr">
+      <c r="A7" s="22" t="inlineStr">
         <is>
           <t>customization options</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>Adjustable volume, behavior modes, routines, app controls</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>1 – 5</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="21" t="inlineStr">
         <is>
           <t>movement level</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>Breathing, head/tail movement, walking/rolling, advanced locomotion</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>1 – 5</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="21" t="inlineStr">
+      <c r="A9" s="22" t="inlineStr">
         <is>
           <t>privacy risk</t>
         </is>
       </c>
-      <c r="B9" s="21" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="C9" s="21" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>Camera, microphone, WiFi, app account, cloud processing</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="D9" s="22" t="inlineStr">
         <is>
           <t>1 – 5
 (reversed:
@@ -1782,22 +1864,22 @@
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="20" t="inlineStr">
+      <c r="A10" s="21" t="inlineStr">
         <is>
           <t>cleanability</t>
         </is>
       </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="C10" s="20" t="inlineStr">
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>How easy it is to wipe, spot-clean, or sanitize</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t>1 – 5
 (floor = 3)</t>
@@ -1805,44 +1887,44 @@
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="21" t="inlineStr">
+      <c r="A11" s="22" t="inlineStr">
         <is>
           <t>durability</t>
         </is>
       </c>
-      <c r="B11" s="21" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="C11" s="21" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>Tolerates frequent handling, drops, or facility use</t>
         </is>
       </c>
-      <c r="D11" s="21" t="inlineStr">
+      <c r="D11" s="22" t="inlineStr">
         <is>
           <t>1 – 5</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="20" t="inlineStr">
+      <c r="A12" s="21" t="inlineStr">
         <is>
           <t>fall-risk profile</t>
         </is>
       </c>
-      <c r="B12" s="20" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="C12" s="20" t="inlineStr">
+      <c r="C12" s="21" t="inlineStr">
         <is>
           <t>Whether the product can get underfoot or create a mobility hazard</t>
         </is>
       </c>
-      <c r="D12" s="20" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t>1 – 5
 (reversed:
@@ -1851,22 +1933,22 @@
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="21" t="inlineStr">
+      <c r="A13" s="22" t="inlineStr">
         <is>
           <t>maintenance requirements</t>
         </is>
       </c>
-      <c r="B13" s="21" t="inlineStr">
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="C13" s="21" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>Batteries, charging, cleaning, software updates, accessories. Includes battery replacement difficulty (moved here from Safety risk).</t>
         </is>
       </c>
-      <c r="D13" s="21" t="inlineStr">
+      <c r="D13" s="22" t="inlineStr">
         <is>
           <t>1 – 5
 (reversed:
@@ -1875,34 +1957,34 @@
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="20" t="inlineStr">
+      <c r="A14" s="21" t="inlineStr">
         <is>
           <t>simplicity of use</t>
         </is>
       </c>
-      <c r="B14" s="20" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="C14" s="20" t="inlineStr">
+      <c r="C14" s="21" t="inlineStr">
         <is>
           <t>How easy to use without instructions after setup</t>
         </is>
       </c>
-      <c r="D14" s="20" t="inlineStr">
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t>1 – 5</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="22" t="inlineStr">
+      <c r="A15" s="23" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B15" s="22" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>100%</t>
         </is>

--- a/Documentation/Best For Lists/Best Pets for Remote Monitoring List.xlsx
+++ b/Documentation/Best For Lists/Best Pets for Remote Monitoring List.xlsx
@@ -623,7 +623,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-15  |  Products shown: 8  |  Eliminated by dedup rule: 5  |  Pre-filter: Type equal Ai &amp; Robotic Pets  (16 products removed)</t>
+          <t>Generated: 2026-07-16  |  Products shown: 8  |  Eliminated by dedup rule: 5  |  Pre-filter: Type equal Ai &amp; Robotic Pets  (16 products removed)</t>
         </is>
       </c>
     </row>

--- a/Documentation/Best For Lists/Best Pets for Remote Monitoring List.xlsx
+++ b/Documentation/Best For Lists/Best Pets for Remote Monitoring List.xlsx
@@ -811,12 +811,12 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Loona</t>
+          <t>Ropet</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Robot Pet Dog</t>
+          <t>KAMOMO</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
@@ -826,57 +826,57 @@
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>Dog</t>
+          <t>Robot</t>
         </is>
       </c>
       <c r="F6" s="9" t="n">
-        <v>499</v>
+        <v>349</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>1199</v>
+        <v>17</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L6" s="9" t="n">
         <v>5</v>
       </c>
       <c r="M6" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N6" s="9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O6" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P6" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q6" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R6" s="9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S6" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T6" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U6" s="8" t="inlineStr">
         <is>
-          <t>KEYi Tech Loona. Rubric anchor product: Control Accessibility=1 (worst) and Customization Options=5 (best). ChatGPT-4o integration. Camera, WiFi, app, account all required. Camera=yes, Internet Access=yes per Product Matrix. Voice=4: excellent AI voice response but conversational not animal-mimicry. Not recommended for seniors or dementia care. Review Strength=4: 1,199 reviews, 4.2★ (repo data, 2026-06-22). DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=1, Familiar Form=2, Safety=2, Calmness=avg(Sound=3, Behavioral Realism=2)=2.5. Raw average of 4 sub-criteria=1.88, rounded=2, Evidence Tier D cap=3 -&gt; Final=2 (was 1). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
+          <t>Founded 2022; CES 2025 debut; Series A1 funded (Beijing AI Industry Investment Fund). Privacy=3: local offline AI for daily use; photo uploads encrypted on-device before cloud (ropetai.com). 39°C bionic warmth feature unique in this market (verified Amazon B0GTPZ4N4M). Stationary desktop companion — no locomotion (Movement=1). Brand Reliability=3: legitimate but newer; 30-day returns per manufacturer. Review strength=3: growing — recommend re-check as product matures. Review Strength=2: 17 reviews, 4.3★ (repo data, 2026-06-22). DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=3, Familiar Form=2, Safety=4, Calmness=avg(Sound=3, Behavioral Realism=2)=2.5. Raw average of 4 sub-criteria=2.88, rounded=3, Evidence Tier D cap=3 -&gt; Final=3 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -886,12 +886,12 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Ropet</t>
+          <t>Loona</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>KAMOMO</t>
+          <t>Robot Pet Dog</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
@@ -901,57 +901,57 @@
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>Robot</t>
+          <t>Dog</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>349</v>
+        <v>499</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H7" s="13" t="n">
-        <v>17</v>
+        <v>1199</v>
       </c>
       <c r="I7" s="14" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="J7" s="13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K7" s="13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M7" s="13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N7" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="O7" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="O7" s="13" t="n">
-        <v>3</v>
-      </c>
       <c r="P7" s="13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q7" s="13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R7" s="13" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S7" s="13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T7" s="13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U7" s="12" t="inlineStr">
         <is>
-          <t>Founded 2022; CES 2025 debut; Series A1 funded (Beijing AI Industry Investment Fund). Privacy=3: local offline AI for daily use; photo uploads encrypted on-device before cloud (ropetai.com). 39°C bionic warmth feature unique in this market (verified Amazon B0GTPZ4N4M). Stationary desktop companion — no locomotion (Movement=1). Brand Reliability=3: legitimate but newer; 30-day returns per manufacturer. Review strength=3: growing — recommend re-check as product matures. Review Strength=2: 17 reviews, 4.3★ (repo data, 2026-06-22). DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=3, Familiar Form=2, Safety=4, Calmness=avg(Sound=3, Behavioral Realism=2)=2.5. Raw average of 4 sub-criteria=2.88, rounded=3, Evidence Tier D cap=3 -&gt; Final=3 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
+          <t>KEYi Tech Loona. Rubric anchor product: Control Accessibility=1 (worst) and Customization Options=5 (best). ChatGPT-4o integration. Camera, WiFi, app, account all required. Camera=yes, Internet Access=yes per Product Matrix. Voice=4: excellent AI voice response but conversational not animal-mimicry. Not recommended for seniors or dementia care. Review Strength=4: 1,199 reviews, 4.2★ (repo data, 2026-06-22). DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=1, Familiar Form=2, Safety=2, Calmness=avg(Sound=3, Behavioral Realism=2)=2.5. Raw average of 4 sub-criteria=1.88, rounded=2, Evidence Tier D cap=3 -&gt; Final=2 (was 1). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>

--- a/Documentation/Best For Lists/Best Pets for Remote Monitoring List.xlsx
+++ b/Documentation/Best For Lists/Best Pets for Remote Monitoring List.xlsx
@@ -623,7 +623,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-16  |  Products shown: 8  |  Eliminated by dedup rule: 5  |  Pre-filter: Type equal Ai &amp; Robotic Pets  (16 products removed)</t>
+          <t>Generated: 2026-08-10  |  Products shown: 8  |  Eliminated by dedup rule: 5  |  Pre-filter: Type equal Ai &amp; Robotic Pets  (16 products removed)</t>
         </is>
       </c>
     </row>
@@ -833,10 +833,10 @@
         <v>349</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="I6" s="10" t="n">
         <v>3.6</v>
@@ -908,10 +908,10 @@
         <v>499</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H7" s="13" t="n">
-        <v>1199</v>
+        <v>1231</v>
       </c>
       <c r="I7" s="14" t="n">
         <v>3.5</v>
@@ -980,13 +980,13 @@
         </is>
       </c>
       <c r="F8" s="9" t="n">
-        <v>50.11</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="G8" s="9" t="n">
         <v>4.8</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>772</v>
+        <v>1132</v>
       </c>
       <c r="I8" s="10" t="n">
         <v>3.35</v>
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>359</v>
+        <v>319</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>5</v>
@@ -1133,10 +1133,10 @@
         <v>69.98999999999999</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>283</v>
+        <v>346</v>
       </c>
       <c r="I10" s="10" t="n">
         <v>3.2</v>
@@ -1205,13 +1205,13 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>179</v>
+        <v>139</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>4.5</v>
       </c>
       <c r="H11" s="13" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I11" s="14" t="n">
         <v>3.1</v>

--- a/Documentation/Best For Lists/Best Pets for Remote Monitoring List.xlsx
+++ b/Documentation/Best For Lists/Best Pets for Remote Monitoring List.xlsx
@@ -623,7 +623,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-08-10  |  Products shown: 8  |  Eliminated by dedup rule: 5  |  Pre-filter: Type equal Ai &amp; Robotic Pets  (16 products removed)</t>
+          <t>Generated: 2026-08-13  |  Products shown: 8  |  Eliminated by dedup rule: 5  |  Pre-filter: Type equal Ai &amp; Robotic Pets  (16 products removed)</t>
         </is>
       </c>
     </row>
